--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jul-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jul-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jul-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jul-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -623,7 +623,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1074,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1063,7 +1091,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1787-42-CM25</t>
+          <t>1079486-82-SE25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,37 +1116,41 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.804.018-8</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>OFISILLAS CHILE SPA</t>
+          <t>COMERCIALIZADORA MERCADO PUBLICO SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.855.435-8</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>76.559.762-5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>13618.8</v>
+        <v>6346.67</v>
       </c>
     </row>
     <row r="12">
@@ -1172,7 +1204,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1269,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1246,7 +1286,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5153-1570-CM25</t>
+          <t>1787-42-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,53 +1301,57 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.804.018-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>76.855.435-8</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>57742.45</v>
+        <v>13618.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5153-1578-CM25</t>
+          <t>5153-1570-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1362,13 +1406,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>56517.15</v>
+        <v>57742.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2182-100-CM25</t>
+          <t>5153-1578-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,27 +1437,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1467,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>28416.68</v>
+        <v>56517.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2328-725-CM25</t>
+          <t>2182-100-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1488,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,43 +1498,47 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11345.98</v>
+        <v>28416.68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5358-210-CM25</t>
+          <t>2328-725-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,48 +1558,52 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.235.755-0</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7445.46</v>
+        <v>11345.98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1375757-25-CM25</t>
+          <t>5358-210-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1576,27 +1628,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1658,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>22120.94</v>
+        <v>7445.46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2421-4025-CM25</t>
+          <t>1375757-25-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1637,43 +1689,47 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CLINICON SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.070.635-1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>10291.28</v>
+        <v>22120.94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1293138-186-CM25</t>
+          <t>2421-4025-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1698,27 +1754,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>CLINICON SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>77.070.635-1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1784,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6295.88</v>
+        <v>10291.28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1417913-149-CM25</t>
+          <t>1293138-186-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,22 +1805,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>70.938.800-2</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,28 +1830,32 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>77.619.564-2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>21179.33</v>
+        <v>6295.88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1426099-143-CM25</t>
+          <t>1417913-149-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1815,48 +1875,52 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>16066.94</v>
+        <v>21179.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1776-53-CM25</t>
+          <t>1426099-143-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1935,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,27 +1945,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.804.017-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Ortopedic</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.765.630-9</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1975,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>5816.99</v>
+        <v>16066.94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2888-39-CM25</t>
+          <t>1776-53-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,27 +2006,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>60.804.017-K</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>Ortopedic</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.765.630-9</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +2036,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7195.48</v>
+        <v>5816.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1360-77-CM25</t>
+          <t>2888-39-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,17 +2067,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.960.900-K</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2026,20 +2090,24 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>20403.96</v>
+        <v>7195.48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1550-20-CM25</t>
+          <t>1360-77-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,43 +2132,47 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>61.960.900-K</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>25027.85</v>
+        <v>20403.96</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2279-570-CM25</t>
+          <t>1550-20-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2125,43 +2197,47 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMMERCE CHILE SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.037.031-0</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>26514.31</v>
+        <v>25027.85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1071775-78-CM25</t>
+          <t>2279-570-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2186,43 +2262,47 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMMERCE CHILE SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>77.037.031-0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>6525.8</v>
+        <v>26514.31</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1698-202-CM25</t>
+          <t>1071775-78-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,53 +2317,57 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>OFISILLAS CHILE SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.855.435-8</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7018.3</v>
+        <v>6525.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4895-118-CM25</t>
+          <t>507428-3246-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2303,48 +2387,52 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>OFISILLAS CHILE SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.855.435-8</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>8503.15</v>
+        <v>41836.08</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>507428-3246-CM25</t>
+          <t>4895-118-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2364,48 +2452,52 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>76.855.435-8</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>41836.08</v>
+        <v>8503.15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3453-329-CM25</t>
+          <t>1698-202-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,53 +2512,57 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>MUNDO LOCKERS SPA</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.580.205-9</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>76.855.435-8</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>20177.42</v>
+        <v>7018.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1346281-110-CM25</t>
+          <t>3453-329-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2491,27 +2587,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MUNDO LOCKERS SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.580.205-9</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2617,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>12456.89</v>
+        <v>20177.42</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5251-1144-CM25</t>
+          <t>1346281-110-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2638,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,43 +2648,47 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>70.729.100-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>14031.92</v>
+        <v>12456.89</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1232565-185-CM25</t>
+          <t>5251-1144-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2613,27 +2713,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>70.729.100-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>INDUMAC LTDA.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>83.732.700-8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2743,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>40144.87</v>
+        <v>14031.92</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5153-1679-CM25</t>
+          <t>1232565-185-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2669,48 +2769,52 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>11002.25</v>
+        <v>40144.87</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5153-1680-CM25</t>
+          <t>5153-1679-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2750,12 +2854,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>77.749.210-1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2869,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>54308.81</v>
+        <v>11002.25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5153-1681-CM25</t>
+          <t>5153-1680-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2811,28 +2915,32 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>55750.63</v>
+        <v>54308.81</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5855-188-CM25</t>
+          <t>5153-1681-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,37 +2955,37 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Camarones</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DIQUALITA SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.050.859-4</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2995,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>8165.93</v>
+        <v>55750.63</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2383-4-CM25</t>
+          <t>5855-188-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2913,32 +3021,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
+          <t>SOCIEDAD COMERCIAL DIQUALITA SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.235.755-0</t>
+          <t>76.050.859-4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +3056,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>49989.9</v>
+        <v>8165.93</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4794-110-CM25</t>
+          <t>1375158-14-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2974,17 +3082,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.001.000-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +3102,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3117,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>26166.24</v>
+        <v>15460.77</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1375158-14-CM25</t>
+          <t>2383-4-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3040,17 +3148,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.001.000-8</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO MEDICO LEGAL</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3070,13 +3178,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>15460.77</v>
+        <v>49989.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1658-3851-CM25</t>
+          <t>4794-110-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,37 +3199,37 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3239,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>20720.3</v>
+        <v>26166.24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1224957-781-CM25</t>
+          <t>1658-3851-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,53 +3260,57 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>70.932.800-K</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA MERCADO PUBLICO SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.559.762-5</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>8329.77</v>
+        <v>20720.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>256-1-CM25</t>
+          <t>1224957-781-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3223,12 +3335,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.932.800-K</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,28 +3350,32 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIALIZADORA MERCADO PUBLICO SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>76.559.762-5</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>25098.81</v>
+        <v>8329.77</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1116007-73-CM25</t>
+          <t>256-1-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,47 +3390,51 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>24753.51</v>
+        <v>25098.81</v>
       </c>
     </row>
     <row r="48">
@@ -3381,7 +3501,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>889473-1434-CM25</t>
+          <t>1116007-73-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,47 +3516,51 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>48172.74</v>
+        <v>24753.51</v>
       </c>
     </row>
     <row r="50">
@@ -3490,7 +3614,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3503,7 +3631,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>608-21463-CM25</t>
+          <t>889473-1434-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3528,43 +3656,47 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>6617.34</v>
+        <v>48172.74</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>979-991-CM25</t>
+          <t>608-21463-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3584,32 +3716,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3751,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>71479.71000000001</v>
+        <v>6617.34</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1293138-180-CM25</t>
+          <t>979-991-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3645,17 +3777,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,28 +3797,32 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>77.043.435-1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>13062.12</v>
+        <v>71479.71000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1293138-148-CM25</t>
+          <t>1293138-180-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3726,28 +3862,32 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.610.398-5</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>77.043.435-1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>10736.19</v>
+        <v>13062.12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1211839-7467-CM25</t>
+          <t>1293138-148-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3772,12 +3912,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>70.856.400-1</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,28 +3927,32 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>77.610.398-5</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>44349.25</v>
+        <v>10736.19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1080157-88-CM25</t>
+          <t>1211839-7467-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3967,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,43 +3977,47 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>70.856.400-1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>MADERERA LAGO VILLARRICA LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>78.616.370-6</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>5944.05</v>
+        <v>44349.25</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>548874-213-CM25</t>
+          <t>1080157-88-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +4032,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,43 +4042,47 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>MADERERA LAGO VILLARRICA LIMITADA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>78.616.370-6</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>40206.68</v>
+        <v>5944.05</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5418-177-CM25</t>
+          <t>548874-213-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3955,43 +4107,47 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>6925.37</v>
+        <v>40206.68</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1057941-2-CM25</t>
+          <t>5418-177-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4016,12 +4172,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.607.507-1</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE P</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,28 +4187,32 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>9243.49</v>
+        <v>6925.37</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1774-131-CM25</t>
+          <t>1057941-2-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4227,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,27 +4237,27 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>61.607.507-1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,7 +4267,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>9897.48</v>
+        <v>9243.49</v>
       </c>
     </row>
     <row r="61">
@@ -4161,7 +4321,11 @@
           <t>77.367.722-0</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4174,7 +4338,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3944-198-CM25</t>
+          <t>1774-131-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,47 +4353,51 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.091.500-6</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERALILLO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>8565.540000000001</v>
+        <v>9897.48</v>
       </c>
     </row>
     <row r="63">
@@ -4344,7 +4512,11 @@
           <t>77.351.814-9</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4577,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4418,61 +4594,130 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>3944-198-CM25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>69.091.500-6</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PERALILLO</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>8565.540000000001</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>889473-1484-CM25</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2239-3-LR23</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>jul-2025</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
         <is>
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>61.980.530-5</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>O'Higgins</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>MELMAN SPA</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="n">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
         <v>14768.11</v>
       </c>
     </row>
